--- a/output/pdf_financials_xlsx/AAZ.xlsx
+++ b/output/pdf_financials_xlsx/AAZ.xlsx
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.805334</v>
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.805334</v>
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.805334</v>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>19.38724</v>
+        <v>-19.38724</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5.326216</v>
+        <v>-5.326216</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6.030562</v>
+        <v>-6.030562</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>20.13335</v>
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.805334</v>
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.805334</v>
@@ -1920,16 +1920,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.06075</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
@@ -4996,37 +4996,37 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.318771</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.8086410000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.844529</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.323401</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.931458</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.395233</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.138388</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>14.767665</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>14.871665</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.401353</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>16.084044</v>
       </c>
     </row>
     <row r="93">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.9693619999999999</v>
@@ -7956,7 +7956,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -8742,7 +8746,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9299,7 +9307,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10107,7 +10119,11 @@
           <t>Reserves (Note 6e))</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -10425,7 +10441,11 @@
           <t>Reserves (Note 6d))</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13665,7 +13685,11 @@
           <t>Reserves (Note 6d) 202,231</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.06075</v>
       </c>
@@ -39061,13 +39085,13 @@
         </is>
       </c>
       <c r="G400" s="5" t="n">
-        <v>0.9693619999999999</v>
+        <v>-0.9693619999999999</v>
       </c>
       <c r="H400" s="5" t="n">
-        <v>2.290273</v>
+        <v>-2.290273</v>
       </c>
       <c r="I400" s="5" t="n">
-        <v>0.482445</v>
+        <v>-0.482445</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -40787,7 +40811,7 @@
         </is>
       </c>
       <c r="F421" s="5" t="n">
-        <v>0.169744</v>
+        <v>-0.169744</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AAZ.xlsx
+++ b/output/pdf_financials_xlsx/AAZ.xlsx
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.005759</v>
+        <v>0.196308</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.266277</v>
+        <v>0.932847</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.7518629999999999</v>
+        <v>4.749746</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.09569</v>
+        <v>0.577599</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.317823</v>
+        <v>0.817334</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>2.536089</v>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.005759</v>
+        <v>-0.196308</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.266277</v>
+        <v>-0.932847</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.7518629999999999</v>
+        <v>-4.749746</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.09569</v>
+        <v>-0.577599</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.317823</v>
+        <v>-0.817334</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-2.536089</v>
@@ -933,37 +933,37 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003485</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010392</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000596</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.010164</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.013057</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.004422</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.085212</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.178862</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.103428</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.042672</v>
       </c>
     </row>
     <row r="13">
@@ -1707,37 +1707,37 @@
         <v>-0.169744</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.9693619999999999</v>
+        <v>-0.965877</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.290273</v>
+        <v>-2.279881</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.482445</v>
+        <v>-0.481849</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.805334</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.460925</v>
+        <v>-2.471089</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.335931</v>
+        <v>-3.348988</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.363265</v>
+        <v>-3.367687</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.649494000000001</v>
+        <v>-9.734705999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.150776</v>
+        <v>-7.329638</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.569528</v>
+        <v>-2.672956</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.175751</v>
+        <v>-3.218423</v>
       </c>
     </row>
     <row r="28">
@@ -1803,37 +1803,37 @@
         <v>-0.169744</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.9693619999999999</v>
+        <v>-0.965877</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.290273</v>
+        <v>-2.279881</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.482445</v>
+        <v>-0.481849</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.805334</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.460925</v>
+        <v>-2.471089</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.335931</v>
+        <v>-3.348988</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.363265</v>
+        <v>-3.367687</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.649494000000001</v>
+        <v>-9.734705999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.150776</v>
+        <v>-7.329638</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.569528</v>
+        <v>-2.672956</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.175751</v>
+        <v>-3.218423</v>
       </c>
     </row>
     <row r="30">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.207196</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -2059,13 +2059,13 @@
         <v>0.108503</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.502158</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.850168</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.514708</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>10.477865</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.207196</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -2155,13 +2155,13 @@
         <v>0.108503</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.502158</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.850168</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.514708</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>10.477865</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.209751</v>
+        <v>0.002555</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -37551,10 +37551,10 @@
         <v>0.577599</v>
       </c>
       <c r="J381" s="5" t="n">
-        <v>-0.817334</v>
+        <v>0.817334</v>
       </c>
       <c r="K381" s="5" t="n">
-        <v>-2.536089</v>
+        <v>2.536089</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -38664,7 +38664,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -40636,7 +40636,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAZ.xlsx
+++ b/output/pdf_financials_xlsx/AAZ.xlsx
@@ -693,37 +693,37 @@
         <v>0.005759</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2165</v>
+        <v>0.377497</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.645718</v>
+        <v>0.965968</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.09569</v>
+        <v>0.229368</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.317823</v>
+        <v>0.659573</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.987359</v>
+        <v>1.518359</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5973039999999999</v>
+        <v>1.307353</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.276496</v>
+        <v>1.170467</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.737306</v>
+        <v>1.514755</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.386602</v>
+        <v>1.19397</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.248571</v>
+        <v>0.866785</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.282966</v>
+        <v>0.824466</v>
       </c>
     </row>
     <row r="8">
@@ -6108,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.242286</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.172306</v>
       </c>
     </row>
     <row r="116">
@@ -14948,7 +14948,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -32947,7 +32951,11 @@
           <t>Consulting and directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -34994,7 +35002,11 @@
           <t>Consulting and directors’ fees (Note 10)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -36114,7 +36126,11 @@
           <t>Consulting and directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -36752,7 +36768,11 @@
           <t>Consulting and directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -38097,7 +38117,11 @@
           <t>Consulting and directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
